--- a/StructureDefinition-stroke-risk-factor-condition-profile.xlsx
+++ b/StructureDefinition-stroke-risk-factor-condition-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07</t>
+    <t>2026-10-27</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,13 +87,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Defines a Condition profile for pre-existing or concurrent conditions that increase stroke risk (e.g., atrial fibrillation/flutter, diabetes, hypertension, coronary disease). The profile fixes category to problem-list-item, binds code (required) to StrokeRiskFactorVS, and supports onset[x] and recordedDate to document chronology and longitudinal tracking. Use this profile to maintain the problem list and to support risk assessment and CDS; do not use it to code the acute stroke event itself.</t>
+    <t>Defines a Condition profile for pre-existing or concurrent conditions and registry-defined assertions that increase stroke risk (e.g., atrial fibrillation/flutter, diabetes, hypertension, coronary disease, smoking within the last 10 years). The profile fixes category to problem-list-item, binds code (required) to StrokeRiskFactorVS, and supports onset[x] and recordedDate to document chronology and longitudinal tracking. Use this profile to maintain the problem list and to support risk assessment and CDS; do not use it to code the acute stroke event itself.</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>To standardize capture of stroke-related risk factor conditions for longitudinal tracking, CDS, and reporting.</t>
+    <t>To standardize capture of stroke-related risk factor conditions and registry-defined assertions for longitudinal tracking, CDS, and reporting.</t>
   </si>
   <si>
     <t>Copyright</t>
